--- a/AAII_Financials/Quarterly/WOOF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WOOF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>WOOF</t>
   </si>
@@ -656,411 +656,436 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43862</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43771</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43680</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1489200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1496700</v>
+      </c>
+      <c r="F8" s="3">
         <v>1515100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1464400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1488500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1493400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1552100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1511400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1523800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1529100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1674500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1494200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1530700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1555900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1578000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1501200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1480800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1476000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1514400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1443300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1434500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1415000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1337700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1260000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2322500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1148700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1093100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2192800</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>898100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>922300</v>
+      </c>
+      <c r="F9" s="3">
         <v>934400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>895400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>903200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>923400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>962900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>935700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>943000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>950500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1068100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>944200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>937700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>951400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>950700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>903500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>886300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>868300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>878900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>848600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>835100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>818000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>768400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>718600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1326500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>650800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>620700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1256500</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>591100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>574400</v>
+      </c>
+      <c r="F10" s="3">
         <v>580800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>569000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>585300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>570000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>589300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>575800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>580700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>578700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>606300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>550000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>593000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>604500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>627300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>597700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>594500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>607700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>635500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>594700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>599400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>597000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>569300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>541400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>996000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>497900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>472400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>936300</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1093,8 +1118,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1185,8 +1212,14 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1277,53 +1310,59 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>3600</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>2700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>1222600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-1500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-2400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1340,87 +1379,93 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>20800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>20600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>15900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>49000</v>
+      </c>
+      <c r="F15" s="3">
         <v>48200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>49800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I15" s="3">
+        <v>49800</v>
+      </c>
+      <c r="J15" s="3">
+        <v>59100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>50100</v>
+      </c>
+      <c r="L15" s="3">
+        <v>49700</v>
+      </c>
+      <c r="M15" s="3">
+        <v>49600</v>
+      </c>
+      <c r="N15" s="3">
+        <v>52200</v>
+      </c>
+      <c r="O15" s="3">
+        <v>50700</v>
+      </c>
+      <c r="P15" s="3">
+        <v>48700</v>
+      </c>
+      <c r="Q15" s="3">
         <v>49300</v>
       </c>
-      <c r="G15" s="3">
-        <v>49400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>59100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>50100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>49700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>49600</v>
-      </c>
-      <c r="L15" s="3">
-        <v>52200</v>
-      </c>
-      <c r="M15" s="3">
-        <v>50700</v>
-      </c>
-      <c r="N15" s="3">
-        <v>48700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>49300</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1434,35 +1479,41 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="3">
         <v>100</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>500</v>
       </c>
       <c r="AA15" s="3">
         <v>200</v>
       </c>
       <c r="AB15" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD15" s="3">
         <v>300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>500</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1492,192 +1543,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1441400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1472100</v>
+      </c>
+      <c r="F17" s="3">
         <v>1481400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1435200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1445500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1477000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1526300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1507500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1521300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1545900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1671500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1503800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1506700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1528300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1500400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1453200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1430800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1426100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1431500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1381300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1361100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1388100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1288300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1214000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2241100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1107500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1069200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2147200</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F18" s="3">
         <v>33800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>29200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>43000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>16400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>25800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-16800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-9600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>24000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>27600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>77600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>48000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>50000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>49900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>82900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>62000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>73400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>26900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>49400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>46000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>81400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>41200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>23900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>45600</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1710,73 +1775,75 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-4600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-12900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-4900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-6200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-3300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-3100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-10100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-30500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>19800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>45200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>300</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1785,393 +1852,423 @@
         <v>300</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>79200</v>
+      </c>
+      <c r="F21" s="3">
         <v>88800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>83900</v>
       </c>
-      <c r="F21" s="3">
-        <v>96400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>70300</v>
-      </c>
       <c r="H21" s="3">
+        <v>96500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>70800</v>
+      </c>
+      <c r="J21" s="3">
         <v>84200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>67000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>56400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>37700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>61300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>44600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>76000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>80000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>125200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>96800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>88500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>97200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>99300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>124500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>159900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>68500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>95600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>89000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>167700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>85200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>67900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>131400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>31600</v>
+        <v>32600</v>
       </c>
       <c r="E22" s="3">
         <v>32800</v>
       </c>
       <c r="F22" s="3">
+        <v>31600</v>
+      </c>
+      <c r="G22" s="3">
+        <v>32800</v>
+      </c>
+      <c r="H22" s="3">
         <v>33300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>33500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>34100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>35800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>36800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>36800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>39700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>36600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>37500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>37200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>32900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>27300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>21800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>19600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>18900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>18800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>19200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>20500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>50000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>53800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>115300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>60800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>63200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>129100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F23" s="3">
         <v>8700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>14700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-11300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-17500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-29500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-51000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-33000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1264000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>42100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>21500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>18100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>30600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>33600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>63000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>99400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>6400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-33600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-19500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-39200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F24" s="3">
         <v>11300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-6300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-4500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-10400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-22900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>14500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>6600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>10000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>9700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>14100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>27000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>10200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-19800</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2262,192 +2359,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>9300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>14000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-11700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-13800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-16700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-46500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-22600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1241100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-14600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>27600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>17300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>11400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>20600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>23900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>48900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>72400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-63500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>9300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>14000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-11700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-13800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-16700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-46500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-22600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1241100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-14600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>32700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>19900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>13500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>24700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>29000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>52800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>75100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>7600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>3400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-28200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-60500</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2538,8 +2653,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2630,8 +2751,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2722,8 +2849,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2814,73 +2947,79 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F32" s="3">
         <v>6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>4600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>12900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>4900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>6200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>3300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>3100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>10100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>30500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-19800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-45200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-300</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -2889,117 +3028,129 @@
         <v>-300</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>9300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>14000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-11700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-13800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-16700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-24800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-46500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-22600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1241100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-14600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>32700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>19900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>13500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>24700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>29000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>52800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>75100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>7600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>3400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-28200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-60500</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3090,197 +3241,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>9300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>14000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-11700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-13800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-16700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-24800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-46500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-22600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1241100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-14600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>32700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>19900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>13500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>24700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>29000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>52800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>75100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>7600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>3400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-28200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-60500</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43862</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43771</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43680</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3313,8 +3482,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3347,86 +3518,88 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>293500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>166800</v>
+      </c>
+      <c r="F41" s="3">
         <v>256700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>237400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>188700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>133300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>165800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>116700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>127600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>89700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>125400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>139800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>173000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>148900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>201900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>148700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>125200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>190900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>211600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>221500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>203400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>174000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>111400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>195800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>168900</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3439,53 +3612,59 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E42" s="3">
+        <v>200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>3700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>4400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3531,86 +3710,92 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>36900</v>
+      </c>
+      <c r="F43" s="3">
         <v>52300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>42900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>34500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>36100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>46500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>40400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>47000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>42100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>50900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>50200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>66300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>45400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>49600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>46400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>44800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>42200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>55600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>45500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>39900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>38100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>41800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>40500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>36700</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,86 +3808,92 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>601600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>632900</v>
+      </c>
+      <c r="F44" s="3">
         <v>590200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>617900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>608500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>645500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>653300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>690300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>672300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>681000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>684500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>730100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>675400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>667900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>652400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>723400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>723300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>682000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>675100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>644400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>628500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>574700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>538700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>541400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>489100</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3715,86 +3906,92 @@
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>58800</v>
+      </c>
+      <c r="F45" s="3">
         <v>56100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>53300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>45800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>32400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>37400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>31800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>28500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>21400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>18900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>33100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>47500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>57700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>112100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>100400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>120500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>133700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>128400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>78500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>72400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>89100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>85600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>96000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>61200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3807,86 +4004,92 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1053100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>960800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1019800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1007400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>939600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>920400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>973600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>931800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>941900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>904100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>951700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1007500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1024800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>976800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1016000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1019000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1013800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1048900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1070800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>989900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>944200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>875900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>777500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>873600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>755900</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3899,8 +4102,14 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3916,35 +4125,35 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>500</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>2600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>1700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3991,86 +4200,92 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1898800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1911200</v>
+      </c>
+      <c r="F48" s="3">
         <v>1944700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1976200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2002100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2004500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2027800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2068200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2128400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2136100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2200400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2218500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2222100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2190500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>2201100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2169900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2150100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>2092200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>2065400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2051700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1968900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1970200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1955700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1996600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>2043400</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4083,8 +4298,14 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4113,56 +4334,56 @@
         <v>2005100</v>
       </c>
       <c r="L49" s="3">
+        <v>2005100</v>
+      </c>
+      <c r="M49" s="3">
+        <v>2005100</v>
+      </c>
+      <c r="N49" s="3">
         <v>2005300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2001200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3221700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3219500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3218900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3216900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3211800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3209000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3209000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3208700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>3208000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>3204900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>3205000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3205200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>3205400</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4396,14 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4267,8 +4494,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4359,86 +4592,92 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>209700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>207500</v>
+      </c>
+      <c r="F52" s="3">
         <v>203800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>216500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>206500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>191200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>187200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>205900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>201200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>211200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>205700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>197600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>192700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>185600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>176800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>171000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>166700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>155700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>152800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>219400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>194100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>142300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>137500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>128400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>120100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4451,8 +4690,14 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4543,86 +4788,92 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5166700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5084600</v>
+      </c>
+      <c r="F54" s="3">
         <v>5173400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>5205100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5153300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5121100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5194400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5211500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5276600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5259000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5363200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5426600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6662300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>6572400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6612800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>6576900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>6542400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>6505800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6497900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>6469500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>6315200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>6193400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>6075700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>6203800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>6124800</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4635,8 +4886,14 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4669,8 +4926,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4703,86 +4962,88 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>455300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>480700</v>
+      </c>
+      <c r="F57" s="3">
         <v>429900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>430000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>423300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>473900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>469700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>447700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>474500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>464500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>410700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>486600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>477700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>393800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>381200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>384600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>416600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>392700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>404000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>380200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>406700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>352400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>339500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>347800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>274200</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4795,86 +5056,92 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>325700</v>
+      </c>
+      <c r="F58" s="3">
         <v>345400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>352400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>312700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>311000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>334900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>346300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>311900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>311700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>400900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>311100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>286500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>288000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>22800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>22600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>22300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>21800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>21800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>20300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>20200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>20200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>2200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>27400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>27600</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4887,86 +5154,92 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>47200</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>41800</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>52400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>617300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>650000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>596600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>597400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>627400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>631100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>582900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>622500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>533600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>558100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>555700</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,86 +5252,92 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1166400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1130300</v>
+      </c>
+      <c r="F60" s="3">
         <v>1134100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1103500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1058600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1083500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1139200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1113700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1117900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1069400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1113100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1114600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1074900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>996900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1021300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1057200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1035400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1011800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1053100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1031500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1009800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>995200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>875300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>933300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>857500</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5071,86 +5350,92 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2468500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2459300</v>
+      </c>
+      <c r="F61" s="3">
         <v>2540800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2618500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2630000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2616400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2623700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2642200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2685900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2667600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2701000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2723900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2749800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2746800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1628300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1631300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1634300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1637400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1640400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1643400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1646500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1649500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1657700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3210300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>3235900</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5163,86 +5448,92 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>104600</v>
+      </c>
+      <c r="F62" s="3">
         <v>99300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>104900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>104600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>106200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>100200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>122000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>121900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>119000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>112900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>124400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>128600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>129800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1581800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1560500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1593500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1568900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1548600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1573700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1499500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1476500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1487400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1514600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1493700</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5255,8 +5546,14 @@
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5347,8 +5644,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5439,8 +5742,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5531,86 +5840,92 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3959700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3929300</v>
+      </c>
+      <c r="F66" s="3">
         <v>4009200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4047500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4014200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4013800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4080800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4088600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4145200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4096700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4178700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4233700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4247500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4171300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4231400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4249000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4263300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4199000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4223900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4232100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4140500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>4106200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>4006900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>5645400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>5575600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5623,8 +5938,14 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5657,8 +5978,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5749,8 +6072,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5841,8 +6170,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5933,8 +6268,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6025,86 +6366,92 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1116500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1155100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1140000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1137400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1146700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1160700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1149100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1135200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1118500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1093700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1047200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1024700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>216500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>231100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>233000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>200200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>180300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>166900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>142200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>113200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>60400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-14700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-800800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-804200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6117,8 +6464,14 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6209,8 +6562,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6301,8 +6660,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6393,86 +6758,92 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1206900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1155300</v>
+      </c>
+      <c r="F76" s="3">
         <v>1164300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1157600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1139100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1107300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1113600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1122800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1131500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1162300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1184400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1192900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2414800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2401100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2381500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2327900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2279100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2306800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2274000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2237400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2174600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2087200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2068800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>558400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>549200</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6485,8 +6856,14 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6577,197 +6954,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43862</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43771</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43680</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>9300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>14000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-11700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-13800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-16700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-24800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-46500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-22600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1241100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-14600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>32700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>19900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>13500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>24700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>29000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>52800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>75100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>7600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-6200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>3400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-28200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-60500</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6800,100 +7195,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>49800</v>
+      </c>
+      <c r="F83" s="3">
         <v>59100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>50100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>49700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>49600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>52200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>50700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>48700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>49300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>50200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>48000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>48600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>47000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>50200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>48000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>48600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>47000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>46800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>42800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>41200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>41600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>45900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>42900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>86000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>43900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>44000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>85600</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6984,8 +7387,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7076,8 +7485,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7168,8 +7583,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7260,8 +7681,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7352,100 +7779,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>161600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="F89" s="3">
         <v>153500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>90100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>85900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-15500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>96000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>20700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>69400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>47000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>34400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>96600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>37700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>136500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>109400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>42600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>57500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>69800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>86000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>87400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>115000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>67100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>109100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>92400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>144600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-29800</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7478,100 +7917,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-37100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-29400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-32100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-28400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-36900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-31000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-27400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-32600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-49100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-62500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-52000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-62100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-65900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-75900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-70300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-65900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-74800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-64400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-52500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-47400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-63300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-37700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-43400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-75800</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7662,8 +8109,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7754,100 +8207,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-37100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-29300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-31000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-27100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-34400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-31400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-26300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-31700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-51300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-50300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-43000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-62800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-67600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-80700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-106000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-65900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-69300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-65200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-55200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-47400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-61300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-47200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-48700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-43800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-75500</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7880,8 +8345,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7921,11 +8388,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7972,8 +8439,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8064,8 +8537,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8156,8 +8635,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8248,100 +8733,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-96400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-3900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-5600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-18300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-28700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-37100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-7100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-15300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-3900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-3700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-4000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-7200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-95500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-120700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>46700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>70900</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8381,11 +8878,11 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8432,96 +8929,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="F102" s="3">
         <v>20000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>59700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>51000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-42900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>60600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-12600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>42800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-45800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-34200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>24900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-62200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>62100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>23900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-70500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-23700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>17200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>28200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>60400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-89600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>29800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>24600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>4100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-34400</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
